--- a/docs/design-sample/DD01_画面一覧.xlsx
+++ b/docs/design-sample/DD01_画面一覧.xlsx
@@ -724,7 +724,7 @@
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="Y25" s="7" t="n"/>
       <c r="Z25" s="7" t="n"/>
@@ -1054,7 +1054,7 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>山田 太郎</t>
         </is>
       </c>
       <c r="AN2" s="7" t="n"/>
@@ -1073,7 +1073,7 @@
       <c r="AW2" s="5" t="n"/>
       <c r="AX2" s="5" t="n"/>
       <c r="AY2" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="AZ2" s="7" t="n"/>
       <c r="BA2" s="7" t="n"/>
@@ -1489,7 +1489,7 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>山田 太郎</t>
         </is>
       </c>
       <c r="AN2" s="7" t="n"/>
@@ -1508,7 +1508,7 @@
       <c r="AW2" s="5" t="n"/>
       <c r="AX2" s="5" t="n"/>
       <c r="AY2" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="AZ2" s="7" t="n"/>
       <c r="BA2" s="7" t="n"/>
@@ -2130,7 +2130,7 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>山田 太郎</t>
         </is>
       </c>
       <c r="AN2" s="7" t="n"/>
@@ -2149,7 +2149,7 @@
       <c r="AW2" s="5" t="n"/>
       <c r="AX2" s="5" t="n"/>
       <c r="AY2" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="AZ2" s="7" t="n"/>
       <c r="BA2" s="7" t="n"/>
